--- a/sources/baek_step8c.xlsx
+++ b/sources/baek_step8c.xlsx
@@ -423,10 +423,10 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col hidden="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col hidden="1" min="10" max="10"/>
@@ -3746,22 +3746,27 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>– 3 [~f_~b]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 ,2 ,3 [~f_~b]</t>
+          <t>1 ,2 ,3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>– High Kick [FLA]</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Double Punch – High Kick [FLA]</t>
+          <t>Double Punch – High Kick</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4159,22 +4164,27 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 ,2 ,3 ,3 ,4 &lt;4 &lt;3 [~f_~b]</t>
+          <t>1 ,2 ,3 ,3 ,4 &lt;4 &lt;3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Double Punch – Black Widow [FLA]</t>
+          <t>Double Punch – Black Widow</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5418,22 +5428,27 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3 ,3 ,4 &lt;4 &lt;3 [~f_~b]</t>
+          <t>3 ,3 ,4 &lt;4 &lt;3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5831,22 +5846,27 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WS+3 ,4 &lt;4 ,3 [~f_~b]</t>
+          <t>WS+3 ,4 &lt;4 ,3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6632,22 +6652,27 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>uf,N,3 ,3 ,4 &lt;4 &lt;3 [~f_~b]</t>
+          <t>uf,N,3 ,3 ,4 &lt;4 &lt;3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baek Hop – Black Widow [FLA]</t>
+          <t>Baek Hop – Black Widow</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7244,27 +7269,32 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>uf+3+4 [f_b]</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7769,22 +7799,27 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>f+4 &lt;3 [f_b]</t>
+          <t>f+4 &lt;3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7978,22 +8013,27 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WS+4 &lt;4 &lt;3 [f_b]</t>
+          <t>WS+4 &lt;4 &lt;3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8187,22 +8227,27 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>df+4 ~4 &lt;3 [f_b]</t>
+          <t>df+4 ~4 &lt;3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8396,27 +8441,32 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FC+4 ,3 ,3 &lt;3 [f_b]</t>
+          <t>FC+4 ,3 ,3 &lt;3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>d+4,3,3&lt;3 [f_b]</t>
+          <t>d+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8672,22 +8722,27 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>(~B)FLA</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9443,22 +9498,27 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3 ,4 ,4 ,3 [f_b]</t>
+          <t>3 ,4 ,4 ,3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9786,22 +9846,27 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -10022,12 +10087,12 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -10269,12 +10334,12 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
@@ -10346,7 +10411,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
@@ -10595,12 +10660,12 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">

--- a/sources/baek_step8c.xlsx
+++ b/sources/baek_step8c.xlsx
@@ -1006,6 +1006,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -1068,6 +1073,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -1128,6 +1138,11 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -10621,6 +10636,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -10666,6 +10686,11 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>hhhlmmmlm!</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
